--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción halpha 2023.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción halpha 2023.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,7 +701,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Octubre 12-2023</t>
+          <t>Septiembre 25-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -715,72 +715,158 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6562.799</v>
+        <v>6562.995</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.9e-06</t>
+          <t>2.8e-05</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-0.58</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-23.63</v>
+        <v>-19.1</v>
       </c>
       <c r="H7" t="n">
-        <v>-22.81</v>
+        <v>-18.04</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="J7" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Septiembre 29-2023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tierra</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Absorción Hα</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6562.986</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2.6e-05</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-18.64</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-18.06</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Octubre 12-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tierra</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Absorción Hα</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6562.799</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-1.9e-06</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-23.63</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-22.81</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Octubre 19-2023</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Tierra</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Absorción Hα</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D10" t="n">
         <v>6562.88</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>1e-05</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F10" t="n">
         <v>3.11</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G10" t="n">
         <v>-17.5</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H10" t="n">
         <v>-19.34</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I10" t="n">
         <v>0.85</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J10" t="n">
         <v>1.11</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K10" t="n">
         <v>1.04</v>
       </c>
     </row>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción halpha 2023.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados absorción halpha 2023.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,7 +701,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Septiembre 25-2023</t>
+          <t>Septiembre 21-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -715,36 +715,36 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6562.995</v>
+        <v>6563.072</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2.8e-05</t>
+          <t>4e-05</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>8.359999999999999</v>
+        <v>11.86</v>
       </c>
       <c r="G7" t="n">
-        <v>-19.1</v>
+        <v>-16.31</v>
       </c>
       <c r="H7" t="n">
-        <v>-18.04</v>
+        <v>-17.55</v>
       </c>
       <c r="I7" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.01</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Septiembre 29-2023</t>
+          <t>Septiembre 25-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -758,36 +758,36 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6562.986</v>
+        <v>6562.995</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2.6e-05</t>
+          <t>2.8e-05</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7.94</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-18.64</v>
+        <v>-19.1</v>
       </c>
       <c r="H8" t="n">
-        <v>-18.06</v>
+        <v>-18.04</v>
       </c>
       <c r="I8" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="J8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Octubre 12-2023</t>
+          <t>Septiembre 29-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -801,72 +801,115 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6562.799</v>
+        <v>6562.986</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-1.9e-06</t>
+          <t>2.6e-05</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-0.58</v>
+        <v>7.94</v>
       </c>
       <c r="G9" t="n">
-        <v>-23.63</v>
+        <v>-18.64</v>
       </c>
       <c r="H9" t="n">
-        <v>-22.81</v>
+        <v>-18.06</v>
       </c>
       <c r="I9" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Octubre 12-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tierra</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Absorción Hα</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6562.799</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-1.9e-06</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-23.63</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-22.81</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Octubre 19-2023</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Tierra</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Absorción Hα</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D11" t="n">
         <v>6562.88</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>1e-05</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F11" t="n">
         <v>3.11</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G11" t="n">
         <v>-17.5</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H11" t="n">
         <v>-19.34</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I11" t="n">
         <v>0.85</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>1.11</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K11" t="n">
         <v>1.04</v>
       </c>
     </row>
